--- a/unit-test-scenarios/통합_테스트_결과서.xlsx
+++ b/unit-test-scenarios/통합_테스트_결과서.xlsx
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>8.029999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:28</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:12.492Z</t>
+          <t>2026-04-09T05:15:33.250Z</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>5.27</v>
+        <v>2.64</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:23.038Z</t>
+          <t>2026-04-09T05:38:20.986Z</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>28.02</v>
+        <v>22.54</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09 12:51:53</t>
+          <t>2026-04-09 14:48:07</t>
         </is>
       </c>
     </row>
@@ -925,11 +925,7 @@
           <t>changeStatus_retiredUser_throwsViaServlet()</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>PATCH /api/users/{id}/status</t>
-        </is>
-      </c>
+      <c r="C3" s="10" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -956,11 +952,7 @@
           <t>changeStatus_success()</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>PATCH /api/users/{id}/status</t>
-        </is>
-      </c>
+      <c r="C4" s="10" t="inlineStr"/>
       <c r="D4" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -987,11 +979,7 @@
           <t>createDepartment_success()</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>POST /api/departments</t>
-        </is>
-      </c>
+      <c r="C5" s="10" t="inlineStr"/>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1018,11 +1006,7 @@
           <t>createPosition_success()</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>POST /api/positions</t>
-        </is>
-      </c>
+      <c r="C6" s="10" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1049,11 +1033,7 @@
           <t>deleteDepartment_hasUsers_throwsViaServlet()</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>DELETE /api/departments/{id}</t>
-        </is>
-      </c>
+      <c r="C7" s="10" t="inlineStr"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1080,11 +1060,7 @@
           <t>deleteDepartment_notFound_throwsViaServlet()</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>DELETE /api/departments/{id}</t>
-        </is>
-      </c>
+      <c r="C8" s="10" t="inlineStr"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1111,11 +1087,7 @@
           <t>deleteDepartment_success()</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>DELETE /api/departments/{id}</t>
-        </is>
-      </c>
+      <c r="C9" s="10" t="inlineStr"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1142,11 +1114,7 @@
           <t>getAllDepartments_success()</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>GET /api/departments</t>
-        </is>
-      </c>
+      <c r="C10" s="10" t="inlineStr"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1173,11 +1141,7 @@
           <t>getAllPositions_success()</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>GET /api/positions</t>
-        </is>
-      </c>
+      <c r="C11" s="10" t="inlineStr"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1204,11 +1168,7 @@
           <t>getCompany_notFound_throwsViaServlet()</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>GET /api/company</t>
-        </is>
-      </c>
+      <c r="C12" s="10" t="inlineStr"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1235,11 +1195,7 @@
           <t>getCompany_success()</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>GET /api/company</t>
-        </is>
-      </c>
+      <c r="C13" s="10" t="inlineStr"/>
       <c r="D13" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1266,11 +1222,7 @@
           <t>updateCompany_allFields()</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>PUT /api/company</t>
-        </is>
-      </c>
+      <c r="C14" s="10" t="inlineStr"/>
       <c r="D14" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1297,11 +1249,7 @@
           <t>updateCompany_allNulls()</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>PUT /api/company</t>
-        </is>
-      </c>
+      <c r="C15" s="10" t="inlineStr"/>
       <c r="D15" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1328,11 +1276,7 @@
           <t>updateCompany_partial()</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>PUT /api/company</t>
-        </is>
-      </c>
+      <c r="C16" s="10" t="inlineStr"/>
       <c r="D16" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1359,11 +1303,7 @@
           <t>updateUser_deptNotFound_throwsViaServlet()</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>PUT /api/users/{id}</t>
-        </is>
-      </c>
+      <c r="C17" s="10" t="inlineStr"/>
       <c r="D17" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1390,11 +1330,7 @@
           <t>updateUser_nullNameAndEmail()</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>PUT /api/users/{id}</t>
-        </is>
-      </c>
+      <c r="C18" s="10" t="inlineStr"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1421,11 +1357,7 @@
           <t>updateUser_posNotFound_throwsViaServlet()</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>PUT /api/users/{id}</t>
-        </is>
-      </c>
+      <c r="C19" s="10" t="inlineStr"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -3440,8 +3372,11 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="잘못된 값" error="PASS, FAIL, ERROR, SKIP 중 하나여야 합니다." promptTitle="결과" prompt="테스트 결과를 선택하세요." type="list">
+      <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3522,12 +3457,12 @@
         </is>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1.099</v>
+        <v>0.663</v>
       </c>
       <c r="F2" s="10" t="inlineStr"/>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:34:57.902Z</t>
+          <t>2026-04-09T05:14:38.552Z</t>
         </is>
       </c>
     </row>
@@ -3549,12 +3484,12 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.064</v>
+        <v>0.079</v>
       </c>
       <c r="F3" s="10" t="inlineStr"/>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:04.279Z</t>
+          <t>2026-04-09T05:15:23.306Z</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3511,12 @@
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.114</v>
+        <v>0.134</v>
       </c>
       <c r="F4" s="10" t="inlineStr"/>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:04.279Z</t>
+          <t>2026-04-09T05:15:23.306Z</t>
         </is>
       </c>
     </row>
@@ -3603,12 +3538,12 @@
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.038</v>
+        <v>0.098</v>
       </c>
       <c r="F5" s="10" t="inlineStr"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:04.279Z</t>
+          <t>2026-04-09T05:15:23.306Z</t>
         </is>
       </c>
     </row>
@@ -3630,12 +3565,12 @@
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.043</v>
+        <v>0.136</v>
       </c>
       <c r="F6" s="10" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:04.279Z</t>
+          <t>2026-04-09T05:15:23.306Z</t>
         </is>
       </c>
     </row>
@@ -3657,12 +3592,12 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.242</v>
+        <v>0.267</v>
       </c>
       <c r="F7" s="10" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:04.279Z</t>
+          <t>2026-04-09T05:15:23.306Z</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3619,12 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.022</v>
+        <v>0.026</v>
       </c>
       <c r="F8" s="10" t="inlineStr"/>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:11.292Z</t>
+          <t>2026-04-09T05:15:32.061Z</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3646,12 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.019</v>
+        <v>0.027</v>
       </c>
       <c r="F9" s="10" t="inlineStr"/>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:11.292Z</t>
+          <t>2026-04-09T05:15:32.061Z</t>
         </is>
       </c>
     </row>
@@ -3738,12 +3673,12 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
       <c r="F10" s="10" t="inlineStr"/>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:11.292Z</t>
+          <t>2026-04-09T05:15:32.061Z</t>
         </is>
       </c>
     </row>
@@ -3765,12 +3700,12 @@
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.8</v>
+        <v>0.758</v>
       </c>
       <c r="F11" s="10" t="inlineStr"/>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:11.292Z</t>
+          <t>2026-04-09T05:15:32.061Z</t>
         </is>
       </c>
     </row>
@@ -3792,12 +3727,12 @@
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.113</v>
+        <v>0.139</v>
       </c>
       <c r="F12" s="10" t="inlineStr"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:11.292Z</t>
+          <t>2026-04-09T05:15:32.061Z</t>
         </is>
       </c>
     </row>
@@ -3819,12 +3754,12 @@
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="F13" s="10" t="inlineStr"/>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:11.292Z</t>
+          <t>2026-04-09T05:15:32.061Z</t>
         </is>
       </c>
     </row>
@@ -3846,12 +3781,12 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.068</v>
+        <v>0.083</v>
       </c>
       <c r="F14" s="10" t="inlineStr"/>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:12.309Z</t>
+          <t>2026-04-09T05:15:33.067Z</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3813,7 @@
       <c r="F15" s="10" t="inlineStr"/>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:12.309Z</t>
+          <t>2026-04-09T05:15:33.067Z</t>
         </is>
       </c>
     </row>
@@ -3900,12 +3835,12 @@
         </is>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="F16" s="10" t="inlineStr"/>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:12.309Z</t>
+          <t>2026-04-09T05:15:33.067Z</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3862,12 @@
         </is>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.038</v>
+        <v>0.027</v>
       </c>
       <c r="F17" s="10" t="inlineStr"/>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:12.309Z</t>
+          <t>2026-04-09T05:15:33.067Z</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3894,7 @@
       <c r="F18" s="10" t="inlineStr"/>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:12.492Z</t>
+          <t>2026-04-09T05:15:33.250Z</t>
         </is>
       </c>
     </row>
@@ -3981,12 +3916,12 @@
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.09</v>
+        <v>0.111</v>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:12.492Z</t>
+          <t>2026-04-09T05:15:33.250Z</t>
         </is>
       </c>
     </row>
@@ -4008,12 +3943,12 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:12.492Z</t>
+          <t>2026-04-09T05:15:33.250Z</t>
         </is>
       </c>
     </row>
@@ -4040,7 +3975,7 @@
       <c r="F21" s="10" t="inlineStr"/>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:12.492Z</t>
+          <t>2026-04-09T05:15:33.250Z</t>
         </is>
       </c>
     </row>
@@ -4062,18 +3997,21 @@
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.034</v>
+        <v>0.019</v>
       </c>
       <c r="F22" s="10" t="inlineStr"/>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:12.492Z</t>
+          <t>2026-04-09T05:15:33.250Z</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="잘못된 값" error="PASS, FAIL, ERROR, SKIP 중 하나여야 합니다." promptTitle="결과" prompt="테스트 결과를 선택하세요." type="list">
+      <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4158,12 +4096,12 @@
         </is>
       </c>
       <c r="E2" s="10" t="n">
-        <v>2.892</v>
+        <v>1.087</v>
       </c>
       <c r="F2" s="10" t="inlineStr"/>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:41.479Z</t>
+          <t>2026-04-09T05:37:49.315Z</t>
         </is>
       </c>
     </row>
@@ -4189,12 +4127,12 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.152</v>
+        <v>0.066</v>
       </c>
       <c r="F3" s="10" t="inlineStr"/>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:44.423Z</t>
+          <t>2026-04-09T05:37:50.431Z</t>
         </is>
       </c>
     </row>
@@ -4216,12 +4154,12 @@
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>1.05</v>
+        <v>0.795</v>
       </c>
       <c r="F4" s="10" t="inlineStr"/>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:56.528Z</t>
+          <t>2026-04-09T05:37:58.376Z</t>
         </is>
       </c>
     </row>
@@ -4243,12 +4181,12 @@
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.181</v>
+        <v>0.16</v>
       </c>
       <c r="F5" s="10" t="inlineStr"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:56.528Z</t>
+          <t>2026-04-09T05:37:58.376Z</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4208,12 @@
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.095</v>
+        <v>0.032</v>
       </c>
       <c r="F6" s="10" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:06.440Z</t>
+          <t>2026-04-09T05:38:05.827Z</t>
         </is>
       </c>
     </row>
@@ -4297,12 +4235,12 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.53</v>
+        <v>0.286</v>
       </c>
       <c r="F7" s="10" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:06.440Z</t>
+          <t>2026-04-09T05:38:05.827Z</t>
         </is>
       </c>
     </row>
@@ -4328,12 +4266,12 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.125</v>
+        <v>0.063</v>
       </c>
       <c r="F8" s="10" t="inlineStr"/>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:07.096Z</t>
+          <t>2026-04-09T05:38:06.158Z</t>
         </is>
       </c>
     </row>
@@ -4355,12 +4293,12 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.038</v>
+        <v>0.032</v>
       </c>
       <c r="F9" s="10" t="inlineStr"/>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:22.993Z</t>
+          <t>2026-04-09T05:38:20.948Z</t>
         </is>
       </c>
     </row>
@@ -4386,12 +4324,12 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.121</v>
+        <v>0.068</v>
       </c>
       <c r="F10" s="10" t="inlineStr"/>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:07.239Z</t>
+          <t>2026-04-09T05:38:06.231Z</t>
         </is>
       </c>
     </row>
@@ -4413,12 +4351,12 @@
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="F11" s="10" t="inlineStr"/>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:23.038Z</t>
+          <t>2026-04-09T05:38:20.986Z</t>
         </is>
       </c>
     </row>
@@ -4444,18 +4382,21 @@
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="F12" s="10" t="inlineStr"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:36:07.376Z</t>
+          <t>2026-04-09T05:38:06.308Z</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="잘못된 값" error="PASS, FAIL, ERROR, SKIP 중 하나여야 합니다." promptTitle="결과" prompt="테스트 결과를 선택하세요." type="list">
+      <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4536,12 +4477,12 @@
         </is>
       </c>
       <c r="E2" s="10" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="F2" s="10" t="inlineStr"/>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:19</t>
+          <t>2026-04-09T05:27:29</t>
         </is>
       </c>
     </row>
@@ -4563,12 +4504,12 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.673</v>
+        <v>0.382</v>
       </c>
       <c r="F3" s="10" t="inlineStr"/>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:19</t>
+          <t>2026-04-09T05:27:29</t>
         </is>
       </c>
     </row>
@@ -4590,12 +4531,12 @@
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.045</v>
+        <v>0.029</v>
       </c>
       <c r="F4" s="10" t="inlineStr"/>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:19</t>
+          <t>2026-04-09T05:27:29</t>
         </is>
       </c>
     </row>
@@ -4617,12 +4558,12 @@
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.051</v>
+        <v>0.033</v>
       </c>
       <c r="F5" s="10" t="inlineStr"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:19</t>
+          <t>2026-04-09T05:27:29</t>
         </is>
       </c>
     </row>
@@ -4644,12 +4585,12 @@
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.255</v>
+        <v>0.103</v>
       </c>
       <c r="F6" s="10" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:19</t>
+          <t>2026-04-09T05:27:29</t>
         </is>
       </c>
     </row>
@@ -4671,12 +4612,12 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.048</v>
+        <v>0.027</v>
       </c>
       <c r="F7" s="10" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:19</t>
+          <t>2026-04-09T05:27:29</t>
         </is>
       </c>
     </row>
@@ -4698,12 +4639,12 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.041</v>
+        <v>0.036</v>
       </c>
       <c r="F8" s="10" t="inlineStr"/>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:19</t>
+          <t>2026-04-09T05:27:29</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4666,12 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1.41</v>
+        <v>0.762</v>
       </c>
       <c r="F9" s="10" t="inlineStr"/>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:19</t>
+          <t>2026-04-09T05:27:29</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4693,12 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.054</v>
+        <v>0.048</v>
       </c>
       <c r="F10" s="10" t="inlineStr"/>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:19</t>
+          <t>2026-04-09T05:27:29</t>
         </is>
       </c>
     </row>
@@ -4779,12 +4720,12 @@
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.042</v>
+        <v>0.033</v>
       </c>
       <c r="F11" s="10" t="inlineStr"/>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:19</t>
+          <t>2026-04-09T05:27:29</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4747,12 @@
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.053</v>
+        <v>0.038</v>
       </c>
       <c r="F12" s="10" t="inlineStr"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:19</t>
+          <t>2026-04-09T05:27:29</t>
         </is>
       </c>
     </row>
@@ -4833,12 +4774,12 @@
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.038</v>
+        <v>0.028</v>
       </c>
       <c r="F13" s="10" t="inlineStr"/>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:19</t>
+          <t>2026-04-09T05:27:29</t>
         </is>
       </c>
     </row>
@@ -4860,12 +4801,12 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="F14" s="10" t="inlineStr"/>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -4887,12 +4828,12 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="F15" s="10" t="inlineStr"/>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -4914,12 +4855,12 @@
         </is>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.022</v>
+        <v>0.013</v>
       </c>
       <c r="F16" s="10" t="inlineStr"/>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4882,12 @@
         </is>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.041</v>
+        <v>0.032</v>
       </c>
       <c r="F17" s="10" t="inlineStr"/>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4909,12 @@
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>0.046</v>
+        <v>0.028</v>
       </c>
       <c r="F18" s="10" t="inlineStr"/>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -4995,12 +4936,12 @@
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.046</v>
+        <v>0.029</v>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5022,12 +4963,12 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.153</v>
+        <v>0.116</v>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5054,7 +4995,7 @@
       <c r="F21" s="10" t="inlineStr"/>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5076,12 +5017,12 @@
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.031</v>
+        <v>0.033</v>
       </c>
       <c r="F22" s="10" t="inlineStr"/>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5103,12 +5044,12 @@
         </is>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.059</v>
+        <v>0.052</v>
       </c>
       <c r="F23" s="10" t="inlineStr"/>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5130,12 +5071,12 @@
         </is>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.06</v>
+        <v>0.108</v>
       </c>
       <c r="F24" s="10" t="inlineStr"/>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5098,12 @@
         </is>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0.094</v>
+        <v>0.064</v>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5125,12 @@
         </is>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.039</v>
+        <v>0.041</v>
       </c>
       <c r="F26" s="10" t="inlineStr"/>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5211,12 +5152,12 @@
         </is>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.044</v>
+        <v>0.032</v>
       </c>
       <c r="F27" s="10" t="inlineStr"/>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5238,12 +5179,12 @@
         </is>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.044</v>
+        <v>0.027</v>
       </c>
       <c r="F28" s="10" t="inlineStr"/>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5265,12 +5206,12 @@
         </is>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.051</v>
+        <v>0.043</v>
       </c>
       <c r="F29" s="10" t="inlineStr"/>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5292,12 +5233,12 @@
         </is>
       </c>
       <c r="E30" s="10" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="F30" s="10" t="inlineStr"/>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5260,12 @@
         </is>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0.04</v>
+        <v>0.031</v>
       </c>
       <c r="F31" s="10" t="inlineStr"/>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5346,12 +5287,12 @@
         </is>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.048</v>
+        <v>0.037</v>
       </c>
       <c r="F32" s="10" t="inlineStr"/>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5373,12 +5314,12 @@
         </is>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.172</v>
+        <v>0.121</v>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5400,12 +5341,12 @@
         </is>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="F34" s="10" t="inlineStr"/>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5368,12 @@
         </is>
       </c>
       <c r="E35" s="10" t="n">
-        <v>0.062</v>
+        <v>0.057</v>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5454,12 +5395,12 @@
         </is>
       </c>
       <c r="E36" s="10" t="n">
-        <v>0.051</v>
+        <v>0.043</v>
       </c>
       <c r="F36" s="10" t="inlineStr"/>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:22</t>
+          <t>2026-04-09T05:27:31</t>
         </is>
       </c>
     </row>
@@ -5481,12 +5422,12 @@
         </is>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.026</v>
+        <v>0.016</v>
       </c>
       <c r="F37" s="10" t="inlineStr"/>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5449,12 @@
         </is>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.032</v>
+        <v>0.011</v>
       </c>
       <c r="F38" s="10" t="inlineStr"/>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -5535,12 +5476,12 @@
         </is>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0.041</v>
+        <v>0.024</v>
       </c>
       <c r="F39" s="10" t="inlineStr"/>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -5562,12 +5503,12 @@
         </is>
       </c>
       <c r="E40" s="10" t="n">
-        <v>0.033</v>
+        <v>0.017</v>
       </c>
       <c r="F40" s="10" t="inlineStr"/>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -5589,12 +5530,12 @@
         </is>
       </c>
       <c r="E41" s="10" t="n">
-        <v>0.035</v>
+        <v>0.011</v>
       </c>
       <c r="F41" s="10" t="inlineStr"/>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -5616,12 +5557,12 @@
         </is>
       </c>
       <c r="E42" s="10" t="n">
-        <v>0.044</v>
+        <v>0.021</v>
       </c>
       <c r="F42" s="10" t="inlineStr"/>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -5643,12 +5584,12 @@
         </is>
       </c>
       <c r="E43" s="10" t="n">
-        <v>0.023</v>
+        <v>0.025</v>
       </c>
       <c r="F43" s="10" t="inlineStr"/>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -5670,12 +5611,12 @@
         </is>
       </c>
       <c r="E44" s="10" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="F44" s="10" t="inlineStr"/>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -5697,12 +5638,12 @@
         </is>
       </c>
       <c r="E45" s="10" t="n">
-        <v>0.022</v>
+        <v>0.015</v>
       </c>
       <c r="F45" s="10" t="inlineStr"/>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -5724,12 +5665,12 @@
         </is>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
       <c r="F46" s="10" t="inlineStr"/>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -5751,12 +5692,12 @@
         </is>
       </c>
       <c r="E47" s="10" t="n">
-        <v>0.037</v>
+        <v>0.029</v>
       </c>
       <c r="F47" s="10" t="inlineStr"/>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -5778,12 +5719,12 @@
         </is>
       </c>
       <c r="E48" s="10" t="n">
-        <v>0.038</v>
+        <v>0.029</v>
       </c>
       <c r="F48" s="10" t="inlineStr"/>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -5805,12 +5746,12 @@
         </is>
       </c>
       <c r="E49" s="10" t="n">
-        <v>0.033</v>
+        <v>0.025</v>
       </c>
       <c r="F49" s="10" t="inlineStr"/>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -5832,12 +5773,12 @@
         </is>
       </c>
       <c r="E50" s="10" t="n">
-        <v>0.032</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="F50" s="10" t="inlineStr"/>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5800,12 @@
         </is>
       </c>
       <c r="E51" s="10" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="F51" s="10" t="inlineStr"/>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -5886,12 +5827,12 @@
         </is>
       </c>
       <c r="E52" s="10" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="F52" s="10" t="inlineStr"/>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -5913,12 +5854,12 @@
         </is>
       </c>
       <c r="E53" s="10" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="F53" s="10" t="inlineStr"/>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5881,12 @@
         </is>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.019</v>
+        <v>0.011</v>
       </c>
       <c r="F54" s="10" t="inlineStr"/>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5908,12 @@
         </is>
       </c>
       <c r="E55" s="10" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="F55" s="10" t="inlineStr"/>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -5994,12 +5935,12 @@
         </is>
       </c>
       <c r="E56" s="10" t="n">
-        <v>0.048</v>
+        <v>0.021</v>
       </c>
       <c r="F56" s="10" t="inlineStr"/>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -6021,12 +5962,12 @@
         </is>
       </c>
       <c r="E57" s="10" t="n">
-        <v>0.028</v>
+        <v>0.014</v>
       </c>
       <c r="F57" s="10" t="inlineStr"/>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -6048,12 +5989,12 @@
         </is>
       </c>
       <c r="E58" s="10" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="F58" s="10" t="inlineStr"/>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6016,12 @@
         </is>
       </c>
       <c r="E59" s="10" t="n">
-        <v>0.029</v>
+        <v>0.021</v>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -6102,12 +6043,12 @@
         </is>
       </c>
       <c r="E60" s="10" t="n">
-        <v>0.079</v>
+        <v>0.035</v>
       </c>
       <c r="F60" s="10" t="inlineStr"/>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -6129,12 +6070,12 @@
         </is>
       </c>
       <c r="E61" s="10" t="n">
-        <v>0.052</v>
+        <v>0.032</v>
       </c>
       <c r="F61" s="10" t="inlineStr"/>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -6156,12 +6097,12 @@
         </is>
       </c>
       <c r="E62" s="10" t="n">
-        <v>0.054</v>
+        <v>0.04</v>
       </c>
       <c r="F62" s="10" t="inlineStr"/>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6124,12 @@
         </is>
       </c>
       <c r="E63" s="10" t="n">
-        <v>0.031</v>
+        <v>0.027</v>
       </c>
       <c r="F63" s="10" t="inlineStr"/>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6151,12 @@
         </is>
       </c>
       <c r="E64" s="10" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.037</v>
       </c>
       <c r="F64" s="10" t="inlineStr"/>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -6237,12 +6178,12 @@
         </is>
       </c>
       <c r="E65" s="10" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="F65" s="10" t="inlineStr"/>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:23</t>
+          <t>2026-04-09T05:27:32</t>
         </is>
       </c>
     </row>
@@ -6264,12 +6205,12 @@
         </is>
       </c>
       <c r="E66" s="10" t="n">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="F66" s="10" t="inlineStr"/>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6237,7 @@
       <c r="F67" s="10" t="inlineStr"/>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -6318,12 +6259,12 @@
         </is>
       </c>
       <c r="E68" s="10" t="n">
-        <v>0.025</v>
+        <v>0.011</v>
       </c>
       <c r="F68" s="10" t="inlineStr"/>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6286,12 @@
         </is>
       </c>
       <c r="E69" s="10" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="F69" s="10" t="inlineStr"/>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6372,12 +6313,12 @@
         </is>
       </c>
       <c r="E70" s="10" t="n">
-        <v>0.038</v>
+        <v>0.019</v>
       </c>
       <c r="F70" s="10" t="inlineStr"/>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6399,12 +6340,12 @@
         </is>
       </c>
       <c r="E71" s="10" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="F71" s="10" t="inlineStr"/>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6367,12 @@
         </is>
       </c>
       <c r="E72" s="10" t="n">
-        <v>0.036</v>
+        <v>0.015</v>
       </c>
       <c r="F72" s="10" t="inlineStr"/>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6453,12 +6394,12 @@
         </is>
       </c>
       <c r="E73" s="10" t="n">
-        <v>0.083</v>
+        <v>0.058</v>
       </c>
       <c r="F73" s="10" t="inlineStr"/>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6480,12 +6421,12 @@
         </is>
       </c>
       <c r="E74" s="10" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="F74" s="10" t="inlineStr"/>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6507,12 +6448,12 @@
         </is>
       </c>
       <c r="E75" s="10" t="n">
-        <v>0.059</v>
+        <v>0.026</v>
       </c>
       <c r="F75" s="10" t="inlineStr"/>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6475,12 @@
         </is>
       </c>
       <c r="E76" s="10" t="n">
-        <v>0.06</v>
+        <v>0.018</v>
       </c>
       <c r="F76" s="10" t="inlineStr"/>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6561,12 +6502,12 @@
         </is>
       </c>
       <c r="E77" s="10" t="n">
-        <v>0.043</v>
+        <v>0.03</v>
       </c>
       <c r="F77" s="10" t="inlineStr"/>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6588,12 +6529,12 @@
         </is>
       </c>
       <c r="E78" s="10" t="n">
-        <v>0.048</v>
+        <v>0.013</v>
       </c>
       <c r="F78" s="10" t="inlineStr"/>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6615,12 +6556,12 @@
         </is>
       </c>
       <c r="E79" s="10" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="F79" s="10" t="inlineStr"/>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6588,7 @@
       <c r="F80" s="10" t="inlineStr"/>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6610,12 @@
         </is>
       </c>
       <c r="E81" s="10" t="n">
-        <v>0.022</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F81" s="10" t="inlineStr"/>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:27</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -6696,12 +6637,12 @@
         </is>
       </c>
       <c r="E82" s="10" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="F82" s="10" t="inlineStr"/>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6728,7 +6669,7 @@
       <c r="F83" s="10" t="inlineStr"/>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6750,12 +6691,12 @@
         </is>
       </c>
       <c r="E84" s="10" t="n">
-        <v>0.027</v>
+        <v>0.022</v>
       </c>
       <c r="F84" s="10" t="inlineStr"/>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6777,12 +6718,12 @@
         </is>
       </c>
       <c r="E85" s="10" t="n">
-        <v>0.026</v>
+        <v>0.016</v>
       </c>
       <c r="F85" s="10" t="inlineStr"/>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6745,12 @@
         </is>
       </c>
       <c r="E86" s="10" t="n">
-        <v>0.066</v>
+        <v>0.028</v>
       </c>
       <c r="F86" s="10" t="inlineStr"/>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6831,12 +6772,12 @@
         </is>
       </c>
       <c r="E87" s="10" t="n">
-        <v>0.102</v>
+        <v>0.042</v>
       </c>
       <c r="F87" s="10" t="inlineStr"/>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6858,12 +6799,12 @@
         </is>
       </c>
       <c r="E88" s="10" t="n">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
       <c r="F88" s="10" t="inlineStr"/>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6826,12 @@
         </is>
       </c>
       <c r="E89" s="10" t="n">
-        <v>0.063</v>
+        <v>0.037</v>
       </c>
       <c r="F89" s="10" t="inlineStr"/>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6853,12 @@
         </is>
       </c>
       <c r="E90" s="10" t="n">
-        <v>0.039</v>
+        <v>0.027</v>
       </c>
       <c r="F90" s="10" t="inlineStr"/>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6939,12 +6880,12 @@
         </is>
       </c>
       <c r="E91" s="10" t="n">
-        <v>0.058</v>
+        <v>0.036</v>
       </c>
       <c r="F91" s="10" t="inlineStr"/>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6966,12 +6907,12 @@
         </is>
       </c>
       <c r="E92" s="10" t="n">
-        <v>0.021</v>
+        <v>0.014</v>
       </c>
       <c r="F92" s="10" t="inlineStr"/>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:24</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -6993,12 +6934,12 @@
         </is>
       </c>
       <c r="E93" s="10" t="n">
-        <v>0.018</v>
+        <v>0.027</v>
       </c>
       <c r="F93" s="10" t="inlineStr"/>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:28</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -7020,12 +6961,12 @@
         </is>
       </c>
       <c r="E94" s="10" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="F94" s="10" t="inlineStr"/>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:28</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -7047,12 +6988,12 @@
         </is>
       </c>
       <c r="E95" s="10" t="n">
-        <v>0.032</v>
+        <v>0.027</v>
       </c>
       <c r="F95" s="10" t="inlineStr"/>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:28</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7015,12 @@
         </is>
       </c>
       <c r="E96" s="10" t="n">
-        <v>0.027</v>
+        <v>0.013</v>
       </c>
       <c r="F96" s="10" t="inlineStr"/>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:28</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7042,12 @@
         </is>
       </c>
       <c r="E97" s="10" t="n">
-        <v>0.751</v>
+        <v>0.62</v>
       </c>
       <c r="F97" s="10" t="inlineStr"/>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:13</t>
+          <t>2026-04-09T05:27:26</t>
         </is>
       </c>
     </row>
@@ -7128,12 +7069,12 @@
         </is>
       </c>
       <c r="E98" s="10" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="F98" s="10" t="inlineStr"/>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -7155,12 +7096,12 @@
         </is>
       </c>
       <c r="E99" s="10" t="n">
-        <v>0.023</v>
+        <v>0.015</v>
       </c>
       <c r="F99" s="10" t="inlineStr"/>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -7187,7 +7128,7 @@
       <c r="F100" s="10" t="inlineStr"/>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7155,7 @@
       <c r="F101" s="10" t="inlineStr"/>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -7236,12 +7177,12 @@
         </is>
       </c>
       <c r="E102" s="10" t="n">
-        <v>0.081</v>
+        <v>0.036</v>
       </c>
       <c r="F102" s="10" t="inlineStr"/>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -7263,12 +7204,12 @@
         </is>
       </c>
       <c r="E103" s="10" t="n">
-        <v>0.037</v>
+        <v>0.029</v>
       </c>
       <c r="F103" s="10" t="inlineStr"/>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -7290,12 +7231,12 @@
         </is>
       </c>
       <c r="E104" s="10" t="n">
-        <v>0.041</v>
+        <v>0.033</v>
       </c>
       <c r="F104" s="10" t="inlineStr"/>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -7317,12 +7258,12 @@
         </is>
       </c>
       <c r="E105" s="10" t="n">
-        <v>0.034</v>
+        <v>0.042</v>
       </c>
       <c r="F105" s="10" t="inlineStr"/>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -7344,12 +7285,12 @@
         </is>
       </c>
       <c r="E106" s="10" t="n">
-        <v>0.046</v>
+        <v>0.052</v>
       </c>
       <c r="F106" s="10" t="inlineStr"/>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -7371,12 +7312,12 @@
         </is>
       </c>
       <c r="E107" s="10" t="n">
-        <v>0.016</v>
+        <v>0.029</v>
       </c>
       <c r="F107" s="10" t="inlineStr"/>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:33</t>
         </is>
       </c>
     </row>
@@ -7398,12 +7339,12 @@
         </is>
       </c>
       <c r="E108" s="10" t="n">
-        <v>0.023</v>
+        <v>0.012</v>
       </c>
       <c r="F108" s="10" t="inlineStr"/>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:28</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -7425,12 +7366,12 @@
         </is>
       </c>
       <c r="E109" s="10" t="n">
-        <v>0.015</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F109" s="10" t="inlineStr"/>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:28</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7393,12 @@
         </is>
       </c>
       <c r="E110" s="10" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F110" s="10" t="inlineStr"/>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:28</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -7479,12 +7420,12 @@
         </is>
       </c>
       <c r="E111" s="10" t="n">
-        <v>0.067</v>
+        <v>0.026</v>
       </c>
       <c r="F111" s="10" t="inlineStr"/>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:34</t>
         </is>
       </c>
     </row>
@@ -7506,12 +7447,12 @@
         </is>
       </c>
       <c r="E112" s="10" t="n">
-        <v>0.053</v>
+        <v>0.018</v>
       </c>
       <c r="F112" s="10" t="inlineStr"/>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:34</t>
         </is>
       </c>
     </row>
@@ -7533,12 +7474,12 @@
         </is>
       </c>
       <c r="E113" s="10" t="n">
-        <v>0.033</v>
+        <v>0.028</v>
       </c>
       <c r="F113" s="10" t="inlineStr"/>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:34</t>
         </is>
       </c>
     </row>
@@ -7560,12 +7501,12 @@
         </is>
       </c>
       <c r="E114" s="10" t="n">
-        <v>0.029</v>
+        <v>0.017</v>
       </c>
       <c r="F114" s="10" t="inlineStr"/>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:34</t>
         </is>
       </c>
     </row>
@@ -7587,12 +7528,12 @@
         </is>
       </c>
       <c r="E115" s="10" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
       <c r="F115" s="10" t="inlineStr"/>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:34</t>
         </is>
       </c>
     </row>
@@ -7614,12 +7555,12 @@
         </is>
       </c>
       <c r="E116" s="10" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="F116" s="10" t="inlineStr"/>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:34</t>
         </is>
       </c>
     </row>
@@ -7641,12 +7582,12 @@
         </is>
       </c>
       <c r="E117" s="10" t="n">
-        <v>0.043</v>
+        <v>0.028</v>
       </c>
       <c r="F117" s="10" t="inlineStr"/>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:34</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7609,12 @@
         </is>
       </c>
       <c r="E118" s="10" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="F118" s="10" t="inlineStr"/>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:34</t>
         </is>
       </c>
     </row>
@@ -7695,12 +7636,12 @@
         </is>
       </c>
       <c r="E119" s="10" t="n">
-        <v>0.048</v>
+        <v>0.025</v>
       </c>
       <c r="F119" s="10" t="inlineStr"/>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:34</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7663,12 @@
         </is>
       </c>
       <c r="E120" s="10" t="n">
-        <v>0.066</v>
+        <v>0.045</v>
       </c>
       <c r="F120" s="10" t="inlineStr"/>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:34</t>
         </is>
       </c>
     </row>
@@ -7749,12 +7690,12 @@
         </is>
       </c>
       <c r="E121" s="10" t="n">
-        <v>0.078</v>
+        <v>0.044</v>
       </c>
       <c r="F121" s="10" t="inlineStr"/>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:34</t>
         </is>
       </c>
     </row>
@@ -7776,12 +7717,12 @@
         </is>
       </c>
       <c r="E122" s="10" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="F122" s="10" t="inlineStr"/>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:25</t>
+          <t>2026-04-09T05:27:34</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7749,7 @@
       <c r="F123" s="10" t="inlineStr"/>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:28</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7771,12 @@
         </is>
       </c>
       <c r="E124" s="10" t="n">
-        <v>0.013</v>
+        <v>0.006</v>
       </c>
       <c r="F124" s="10" t="inlineStr"/>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:28</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -7857,12 +7798,12 @@
         </is>
       </c>
       <c r="E125" s="10" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="F125" s="10" t="inlineStr"/>
       <c r="G125" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:28</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
@@ -7884,18 +7825,21 @@
         </is>
       </c>
       <c r="E126" s="10" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="F126" s="10" t="inlineStr"/>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T03:35:28</t>
+          <t>2026-04-09T05:27:35</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="잘못된 값" error="PASS, FAIL, ERROR, SKIP 중 하나여야 합니다." promptTitle="결과" prompt="테스트 결과를 선택하세요." type="list">
+      <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
     </dataValidation>
   </dataValidations>

--- a/unit-test-scenarios/통합_테스트_결과서.xlsx
+++ b/unit-test-scenarios/통합_테스트_결과서.xlsx
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>5.4</v>
+        <v>10.54</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>2.74</v>
+        <v>2.16</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:33.250Z</t>
+          <t>2026-04-09T06:49:13.844Z</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2.64</v>
+        <v>8</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09T05:38:20.986Z</t>
+          <t>2026-04-09T06:49:23.440Z</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>22.54</v>
+        <v>32.46</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09 14:48:07</t>
+          <t>2026-04-09 16:18:17</t>
         </is>
       </c>
     </row>
@@ -3372,8 +3372,11 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="잘못된 값" error="PASS, FAIL, ERROR, SKIP 중 하나여야 합니다." promptTitle="결과" prompt="테스트 결과를 선택하세요." type="list">
+      <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -3457,12 +3460,12 @@
         </is>
       </c>
       <c r="E2" s="10" t="n">
-        <v>0.663</v>
+        <v>0.017</v>
       </c>
       <c r="F2" s="10" t="inlineStr"/>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:14:38.552Z</t>
+          <t>2026-04-09T06:48:24.797Z</t>
         </is>
       </c>
     </row>
@@ -3484,12 +3487,12 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.079</v>
+        <v>0.068</v>
       </c>
       <c r="F3" s="10" t="inlineStr"/>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:23.306Z</t>
+          <t>2026-04-09T06:49:03.001Z</t>
         </is>
       </c>
     </row>
@@ -3511,12 +3514,12 @@
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.134</v>
+        <v>0.137</v>
       </c>
       <c r="F4" s="10" t="inlineStr"/>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:23.306Z</t>
+          <t>2026-04-09T06:49:03.001Z</t>
         </is>
       </c>
     </row>
@@ -3538,12 +3541,12 @@
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.098</v>
+        <v>0.045</v>
       </c>
       <c r="F5" s="10" t="inlineStr"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:23.306Z</t>
+          <t>2026-04-09T06:49:03.001Z</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3568,12 @@
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.136</v>
+        <v>0.03</v>
       </c>
       <c r="F6" s="10" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:23.306Z</t>
+          <t>2026-04-09T06:49:03.001Z</t>
         </is>
       </c>
     </row>
@@ -3592,12 +3595,12 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.267</v>
+        <v>0.237</v>
       </c>
       <c r="F7" s="10" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:23.306Z</t>
+          <t>2026-04-09T06:49:03.001Z</t>
         </is>
       </c>
     </row>
@@ -3619,12 +3622,12 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.026</v>
+        <v>0.022</v>
       </c>
       <c r="F8" s="10" t="inlineStr"/>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:32.061Z</t>
+          <t>2026-04-09T06:49:12.513Z</t>
         </is>
       </c>
     </row>
@@ -3646,12 +3649,12 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="F9" s="10" t="inlineStr"/>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:32.061Z</t>
+          <t>2026-04-09T06:49:12.513Z</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3681,7 @@
       <c r="F10" s="10" t="inlineStr"/>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:32.061Z</t>
+          <t>2026-04-09T06:49:12.513Z</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3703,12 @@
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.758</v>
+        <v>0.89</v>
       </c>
       <c r="F11" s="10" t="inlineStr"/>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:32.061Z</t>
+          <t>2026-04-09T06:49:12.513Z</t>
         </is>
       </c>
     </row>
@@ -3727,12 +3730,12 @@
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.139</v>
+        <v>0.136</v>
       </c>
       <c r="F12" s="10" t="inlineStr"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:32.061Z</t>
+          <t>2026-04-09T06:49:12.513Z</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3757,12 @@
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="F13" s="10" t="inlineStr"/>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:32.061Z</t>
+          <t>2026-04-09T06:49:12.513Z</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3784,12 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.083</v>
+        <v>0.102</v>
       </c>
       <c r="F14" s="10" t="inlineStr"/>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:33.067Z</t>
+          <t>2026-04-09T06:49:13.643Z</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3811,12 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="F15" s="10" t="inlineStr"/>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:33.067Z</t>
+          <t>2026-04-09T06:49:13.643Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3843,7 @@
       <c r="F16" s="10" t="inlineStr"/>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:33.067Z</t>
+          <t>2026-04-09T06:49:13.643Z</t>
         </is>
       </c>
     </row>
@@ -3862,12 +3865,12 @@
         </is>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.027</v>
+        <v>0.031</v>
       </c>
       <c r="F17" s="10" t="inlineStr"/>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:33.067Z</t>
+          <t>2026-04-09T06:49:13.643Z</t>
         </is>
       </c>
     </row>
@@ -3889,12 +3892,12 @@
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>0.039</v>
+        <v>0.113</v>
       </c>
       <c r="F18" s="10" t="inlineStr"/>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:33.250Z</t>
+          <t>2026-04-09T06:49:13.844Z</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3919,12 @@
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.111</v>
+        <v>0.11</v>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:33.250Z</t>
+          <t>2026-04-09T06:49:13.844Z</t>
         </is>
       </c>
     </row>
@@ -3943,12 +3946,12 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.02</v>
+        <v>0.045</v>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:33.250Z</t>
+          <t>2026-04-09T06:49:13.844Z</t>
         </is>
       </c>
     </row>
@@ -3970,12 +3973,12 @@
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.019</v>
+        <v>0.035</v>
       </c>
       <c r="F21" s="10" t="inlineStr"/>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:33.250Z</t>
+          <t>2026-04-09T06:49:13.844Z</t>
         </is>
       </c>
     </row>
@@ -3997,18 +4000,21 @@
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.019</v>
+        <v>0.029</v>
       </c>
       <c r="F22" s="10" t="inlineStr"/>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:15:33.250Z</t>
+          <t>2026-04-09T06:49:13.844Z</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="잘못된 값" error="PASS, FAIL, ERROR, SKIP 중 하나여야 합니다." promptTitle="결과" prompt="테스트 결과를 선택하세요." type="list">
+      <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -4085,23 +4091,19 @@
           <t>결재 요청 생성 API는 H2에 approval request를 저장한다</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>POST /api/approval-requests</t>
-        </is>
-      </c>
+      <c r="C2" s="10" t="inlineStr"/>
       <c r="D2" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1.087</v>
+        <v>4.452</v>
       </c>
       <c r="F2" s="10" t="inlineStr"/>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:37:49.315Z</t>
+          <t>2026-04-09T06:48:44.863Z</t>
         </is>
       </c>
     </row>
@@ -4116,23 +4118,19 @@
           <t>수금 처리 API는 실제 DB 상태와 수금일을 변경한다</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>PUT /api/collections/{collectionId}</t>
-        </is>
-      </c>
+      <c r="C3" s="10" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.066</v>
+        <v>0.272</v>
       </c>
       <c r="F3" s="10" t="inlineStr"/>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:37:50.431Z</t>
+          <t>2026-04-09T06:48:49.373Z</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4152,12 @@
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.795</v>
+        <v>2.109</v>
       </c>
       <c r="F4" s="10" t="inlineStr"/>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:37:58.376Z</t>
+          <t>2026-04-09T06:49:04.576Z</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4179,12 @@
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.16</v>
+        <v>0.244</v>
       </c>
       <c r="F5" s="10" t="inlineStr"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:37:58.376Z</t>
+          <t>2026-04-09T06:49:04.576Z</t>
         </is>
       </c>
     </row>
@@ -4208,12 +4206,12 @@
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.032</v>
+        <v>0.049</v>
       </c>
       <c r="F6" s="10" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:38:05.827Z</t>
+          <t>2026-04-09T06:49:15.878Z</t>
         </is>
       </c>
     </row>
@@ -4235,12 +4233,12 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.286</v>
+        <v>0.575</v>
       </c>
       <c r="F7" s="10" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:38:05.827Z</t>
+          <t>2026-04-09T06:49:15.878Z</t>
         </is>
       </c>
     </row>
@@ -4255,23 +4253,19 @@
           <t>생산지시서 목록 조회 API는 H2에 저장된 데이터를 반환한다</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>GET /api/production-orders</t>
-        </is>
-      </c>
+      <c r="C8" s="10" t="inlineStr"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.063</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F8" s="10" t="inlineStr"/>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:38:06.158Z</t>
+          <t>2026-04-09T06:49:16.526Z</t>
         </is>
       </c>
     </row>
@@ -4293,12 +4287,12 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.032</v>
+        <v>0.056</v>
       </c>
       <c r="F9" s="10" t="inlineStr"/>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:38:20.948Z</t>
+          <t>2026-04-09T06:49:23.374Z</t>
         </is>
       </c>
     </row>
@@ -4313,23 +4307,19 @@
           <t>PI 생성 API는 프론트에서 전달한 환율로 KRW 품목단가를 외화로 환산해 저장한다</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>POST /api/proforma-invoices</t>
-        </is>
-      </c>
+      <c r="C10" s="10" t="inlineStr"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.068</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F10" s="10" t="inlineStr"/>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:38:06.231Z</t>
+          <t>2026-04-09T06:49:16.610Z</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4341,12 @@
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.015</v>
+        <v>0.031</v>
       </c>
       <c r="F11" s="10" t="inlineStr"/>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:38:20.986Z</t>
+          <t>2026-04-09T06:49:23.440Z</t>
         </is>
       </c>
     </row>
@@ -4371,29 +4361,28 @@
           <t>출하현황 상태 변경 API는 실제 DB 상태를 변경한다</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>PUT /api/shipments/{id}</t>
-        </is>
-      </c>
+      <c r="C12" s="10" t="inlineStr"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.035</v>
+        <v>0.05</v>
       </c>
       <c r="F12" s="10" t="inlineStr"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:38:06.308Z</t>
+          <t>2026-04-09T06:49:16.713Z</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="잘못된 값" error="PASS, FAIL, ERROR, SKIP 중 하나여야 합니다." promptTitle="결과" prompt="테스트 결과를 선택하세요." type="list">
+      <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -4477,12 +4466,12 @@
         </is>
       </c>
       <c r="E2" s="10" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="F2" s="10" t="inlineStr"/>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:29</t>
+          <t>2026-04-09T06:42:33</t>
         </is>
       </c>
     </row>
@@ -4504,12 +4493,12 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.382</v>
+        <v>0.487</v>
       </c>
       <c r="F3" s="10" t="inlineStr"/>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:29</t>
+          <t>2026-04-09T06:42:33</t>
         </is>
       </c>
     </row>
@@ -4531,12 +4520,12 @@
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.029</v>
+        <v>0.094</v>
       </c>
       <c r="F4" s="10" t="inlineStr"/>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:29</t>
+          <t>2026-04-09T06:42:33</t>
         </is>
       </c>
     </row>
@@ -4558,12 +4547,12 @@
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.033</v>
+        <v>0.062</v>
       </c>
       <c r="F5" s="10" t="inlineStr"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:29</t>
+          <t>2026-04-09T06:42:33</t>
         </is>
       </c>
     </row>
@@ -4585,12 +4574,12 @@
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.103</v>
+        <v>0.105</v>
       </c>
       <c r="F6" s="10" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:29</t>
+          <t>2026-04-09T06:42:33</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4601,12 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="F7" s="10" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:29</t>
+          <t>2026-04-09T06:42:33</t>
         </is>
       </c>
     </row>
@@ -4639,12 +4628,12 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.036</v>
+        <v>0.078</v>
       </c>
       <c r="F8" s="10" t="inlineStr"/>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:29</t>
+          <t>2026-04-09T06:42:33</t>
         </is>
       </c>
     </row>
@@ -4666,12 +4655,12 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.762</v>
+        <v>1.364</v>
       </c>
       <c r="F9" s="10" t="inlineStr"/>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:29</t>
+          <t>2026-04-09T06:42:33</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4682,12 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.048</v>
+        <v>0.116</v>
       </c>
       <c r="F10" s="10" t="inlineStr"/>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:29</t>
+          <t>2026-04-09T06:42:33</t>
         </is>
       </c>
     </row>
@@ -4720,12 +4709,12 @@
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.033</v>
+        <v>0.059</v>
       </c>
       <c r="F11" s="10" t="inlineStr"/>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:29</t>
+          <t>2026-04-09T06:42:33</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4741,7 @@
       <c r="F12" s="10" t="inlineStr"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:29</t>
+          <t>2026-04-09T06:42:33</t>
         </is>
       </c>
     </row>
@@ -4774,12 +4763,12 @@
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.028</v>
+        <v>0.034</v>
       </c>
       <c r="F13" s="10" t="inlineStr"/>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:29</t>
+          <t>2026-04-09T06:42:33</t>
         </is>
       </c>
     </row>
@@ -4801,12 +4790,12 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="F14" s="10" t="inlineStr"/>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:42</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4817,12 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="F15" s="10" t="inlineStr"/>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:42</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4844,12 @@
         </is>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="F16" s="10" t="inlineStr"/>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:42</t>
         </is>
       </c>
     </row>
@@ -4882,12 +4871,12 @@
         </is>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.032</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F17" s="10" t="inlineStr"/>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -4909,12 +4898,12 @@
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>0.028</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F18" s="10" t="inlineStr"/>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4925,12 @@
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.029</v>
+        <v>0.078</v>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -4963,12 +4952,12 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.116</v>
+        <v>0.222</v>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -4990,12 +4979,12 @@
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.031</v>
+        <v>0.053</v>
       </c>
       <c r="F21" s="10" t="inlineStr"/>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5017,12 +5006,12 @@
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.033</v>
+        <v>0.055</v>
       </c>
       <c r="F22" s="10" t="inlineStr"/>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5033,12 @@
         </is>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.052</v>
+        <v>0.109</v>
       </c>
       <c r="F23" s="10" t="inlineStr"/>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5060,12 @@
         </is>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.108</v>
+        <v>0.186</v>
       </c>
       <c r="F24" s="10" t="inlineStr"/>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5087,12 @@
         </is>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0.064</v>
+        <v>0.17</v>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5125,12 +5114,12 @@
         </is>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.041</v>
+        <v>0.067</v>
       </c>
       <c r="F26" s="10" t="inlineStr"/>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5141,12 @@
         </is>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.032</v>
+        <v>0.215</v>
       </c>
       <c r="F27" s="10" t="inlineStr"/>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5179,12 +5168,12 @@
         </is>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.027</v>
+        <v>0.291</v>
       </c>
       <c r="F28" s="10" t="inlineStr"/>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5206,12 +5195,12 @@
         </is>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.043</v>
+        <v>0.08</v>
       </c>
       <c r="F29" s="10" t="inlineStr"/>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5233,12 +5222,12 @@
         </is>
       </c>
       <c r="E30" s="10" t="n">
-        <v>0.076</v>
+        <v>0.227</v>
       </c>
       <c r="F30" s="10" t="inlineStr"/>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5260,12 +5249,12 @@
         </is>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0.031</v>
+        <v>0.067</v>
       </c>
       <c r="F31" s="10" t="inlineStr"/>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5276,12 @@
         </is>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.037</v>
+        <v>0.141</v>
       </c>
       <c r="F32" s="10" t="inlineStr"/>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5314,12 +5303,12 @@
         </is>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.121</v>
+        <v>0.262</v>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5341,12 +5330,12 @@
         </is>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.03</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F34" s="10" t="inlineStr"/>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5368,12 +5357,12 @@
         </is>
       </c>
       <c r="E35" s="10" t="n">
-        <v>0.057</v>
+        <v>0.146</v>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5384,12 @@
         </is>
       </c>
       <c r="E36" s="10" t="n">
-        <v>0.043</v>
+        <v>0.117</v>
       </c>
       <c r="F36" s="10" t="inlineStr"/>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:31</t>
+          <t>2026-04-09T06:42:35</t>
         </is>
       </c>
     </row>
@@ -5422,12 +5411,12 @@
         </is>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.016</v>
+        <v>0.024</v>
       </c>
       <c r="F37" s="10" t="inlineStr"/>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:42</t>
         </is>
       </c>
     </row>
@@ -5449,12 +5438,12 @@
         </is>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.011</v>
+        <v>0.049</v>
       </c>
       <c r="F38" s="10" t="inlineStr"/>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:42</t>
         </is>
       </c>
     </row>
@@ -5476,12 +5465,12 @@
         </is>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0.024</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F39" s="10" t="inlineStr"/>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:42</t>
         </is>
       </c>
     </row>
@@ -5503,12 +5492,12 @@
         </is>
       </c>
       <c r="E40" s="10" t="n">
-        <v>0.017</v>
+        <v>0.03</v>
       </c>
       <c r="F40" s="10" t="inlineStr"/>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:42</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5519,12 @@
         </is>
       </c>
       <c r="E41" s="10" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="F41" s="10" t="inlineStr"/>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:42</t>
         </is>
       </c>
     </row>
@@ -5557,12 +5546,12 @@
         </is>
       </c>
       <c r="E42" s="10" t="n">
-        <v>0.021</v>
+        <v>0.063</v>
       </c>
       <c r="F42" s="10" t="inlineStr"/>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:38</t>
         </is>
       </c>
     </row>
@@ -5584,12 +5573,12 @@
         </is>
       </c>
       <c r="E43" s="10" t="n">
-        <v>0.025</v>
+        <v>0.041</v>
       </c>
       <c r="F43" s="10" t="inlineStr"/>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:38</t>
         </is>
       </c>
     </row>
@@ -5611,12 +5600,12 @@
         </is>
       </c>
       <c r="E44" s="10" t="n">
-        <v>0.021</v>
+        <v>0.03</v>
       </c>
       <c r="F44" s="10" t="inlineStr"/>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:38</t>
         </is>
       </c>
     </row>
@@ -5638,12 +5627,12 @@
         </is>
       </c>
       <c r="E45" s="10" t="n">
-        <v>0.015</v>
+        <v>0.041</v>
       </c>
       <c r="F45" s="10" t="inlineStr"/>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:38</t>
         </is>
       </c>
     </row>
@@ -5665,12 +5654,12 @@
         </is>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.039</v>
+        <v>0.126</v>
       </c>
       <c r="F46" s="10" t="inlineStr"/>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:38</t>
         </is>
       </c>
     </row>
@@ -5692,12 +5681,12 @@
         </is>
       </c>
       <c r="E47" s="10" t="n">
-        <v>0.029</v>
+        <v>0.052</v>
       </c>
       <c r="F47" s="10" t="inlineStr"/>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:38</t>
         </is>
       </c>
     </row>
@@ -5719,12 +5708,12 @@
         </is>
       </c>
       <c r="E48" s="10" t="n">
-        <v>0.029</v>
+        <v>0.064</v>
       </c>
       <c r="F48" s="10" t="inlineStr"/>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:38</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5735,12 @@
         </is>
       </c>
       <c r="E49" s="10" t="n">
-        <v>0.025</v>
+        <v>0.038</v>
       </c>
       <c r="F49" s="10" t="inlineStr"/>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:38</t>
         </is>
       </c>
     </row>
@@ -5773,12 +5762,12 @@
         </is>
       </c>
       <c r="E50" s="10" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="F50" s="10" t="inlineStr"/>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:38</t>
         </is>
       </c>
     </row>
@@ -5800,12 +5789,12 @@
         </is>
       </c>
       <c r="E51" s="10" t="n">
-        <v>0.042</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="F51" s="10" t="inlineStr"/>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:38</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5816,12 @@
         </is>
       </c>
       <c r="E52" s="10" t="n">
-        <v>0.017</v>
+        <v>0.028</v>
       </c>
       <c r="F52" s="10" t="inlineStr"/>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:38</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5843,12 @@
         </is>
       </c>
       <c r="E53" s="10" t="n">
-        <v>0.011</v>
+        <v>0.017</v>
       </c>
       <c r="F53" s="10" t="inlineStr"/>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5870,12 @@
         </is>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.011</v>
+        <v>0.054</v>
       </c>
       <c r="F54" s="10" t="inlineStr"/>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -5908,12 +5897,12 @@
         </is>
       </c>
       <c r="E55" s="10" t="n">
-        <v>0.007</v>
+        <v>0.017</v>
       </c>
       <c r="F55" s="10" t="inlineStr"/>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -5935,12 +5924,12 @@
         </is>
       </c>
       <c r="E56" s="10" t="n">
-        <v>0.021</v>
+        <v>0.066</v>
       </c>
       <c r="F56" s="10" t="inlineStr"/>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5951,12 @@
         </is>
       </c>
       <c r="E57" s="10" t="n">
-        <v>0.014</v>
+        <v>0.031</v>
       </c>
       <c r="F57" s="10" t="inlineStr"/>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -5989,12 +5978,12 @@
         </is>
       </c>
       <c r="E58" s="10" t="n">
-        <v>0.02</v>
+        <v>0.054</v>
       </c>
       <c r="F58" s="10" t="inlineStr"/>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6016,12 +6005,12 @@
         </is>
       </c>
       <c r="E59" s="10" t="n">
-        <v>0.021</v>
+        <v>0.03</v>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6043,12 +6032,12 @@
         </is>
       </c>
       <c r="E60" s="10" t="n">
-        <v>0.035</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F60" s="10" t="inlineStr"/>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6070,12 +6059,12 @@
         </is>
       </c>
       <c r="E61" s="10" t="n">
-        <v>0.032</v>
+        <v>0.046</v>
       </c>
       <c r="F61" s="10" t="inlineStr"/>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6086,12 @@
         </is>
       </c>
       <c r="E62" s="10" t="n">
-        <v>0.04</v>
+        <v>0.051</v>
       </c>
       <c r="F62" s="10" t="inlineStr"/>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6124,12 +6113,12 @@
         </is>
       </c>
       <c r="E63" s="10" t="n">
-        <v>0.027</v>
+        <v>0.033</v>
       </c>
       <c r="F63" s="10" t="inlineStr"/>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6151,12 +6140,12 @@
         </is>
       </c>
       <c r="E64" s="10" t="n">
-        <v>0.037</v>
+        <v>0.089</v>
       </c>
       <c r="F64" s="10" t="inlineStr"/>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6178,12 +6167,12 @@
         </is>
       </c>
       <c r="E65" s="10" t="n">
-        <v>0.017</v>
+        <v>0.027</v>
       </c>
       <c r="F65" s="10" t="inlineStr"/>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:32</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6205,12 +6194,12 @@
         </is>
       </c>
       <c r="E66" s="10" t="n">
-        <v>0.006</v>
+        <v>0.045</v>
       </c>
       <c r="F66" s="10" t="inlineStr"/>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -6232,12 +6221,12 @@
         </is>
       </c>
       <c r="E67" s="10" t="n">
-        <v>0.028</v>
+        <v>0.049</v>
       </c>
       <c r="F67" s="10" t="inlineStr"/>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -6259,12 +6248,12 @@
         </is>
       </c>
       <c r="E68" s="10" t="n">
-        <v>0.011</v>
+        <v>0.019</v>
       </c>
       <c r="F68" s="10" t="inlineStr"/>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -6286,12 +6275,12 @@
         </is>
       </c>
       <c r="E69" s="10" t="n">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
       <c r="F69" s="10" t="inlineStr"/>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6302,12 @@
         </is>
       </c>
       <c r="E70" s="10" t="n">
-        <v>0.019</v>
+        <v>0.028</v>
       </c>
       <c r="F70" s="10" t="inlineStr"/>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6340,12 +6329,12 @@
         </is>
       </c>
       <c r="E71" s="10" t="n">
-        <v>0.02</v>
+        <v>0.039</v>
       </c>
       <c r="F71" s="10" t="inlineStr"/>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6367,12 +6356,12 @@
         </is>
       </c>
       <c r="E72" s="10" t="n">
-        <v>0.015</v>
+        <v>0.042</v>
       </c>
       <c r="F72" s="10" t="inlineStr"/>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6394,12 +6383,12 @@
         </is>
       </c>
       <c r="E73" s="10" t="n">
-        <v>0.058</v>
+        <v>0.12</v>
       </c>
       <c r="F73" s="10" t="inlineStr"/>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6410,12 @@
         </is>
       </c>
       <c r="E74" s="10" t="n">
-        <v>0.021</v>
+        <v>0.026</v>
       </c>
       <c r="F74" s="10" t="inlineStr"/>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6442,7 @@
       <c r="F75" s="10" t="inlineStr"/>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6475,12 +6464,12 @@
         </is>
       </c>
       <c r="E76" s="10" t="n">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
       <c r="F76" s="10" t="inlineStr"/>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6491,12 @@
         </is>
       </c>
       <c r="E77" s="10" t="n">
-        <v>0.03</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F77" s="10" t="inlineStr"/>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6518,12 @@
         </is>
       </c>
       <c r="E78" s="10" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="F78" s="10" t="inlineStr"/>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:39</t>
         </is>
       </c>
     </row>
@@ -6556,12 +6545,12 @@
         </is>
       </c>
       <c r="E79" s="10" t="n">
-        <v>0.011</v>
+        <v>0.028</v>
       </c>
       <c r="F79" s="10" t="inlineStr"/>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -6583,12 +6572,12 @@
         </is>
       </c>
       <c r="E80" s="10" t="n">
-        <v>0.012</v>
+        <v>0.027</v>
       </c>
       <c r="F80" s="10" t="inlineStr"/>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -6610,12 +6599,12 @@
         </is>
       </c>
       <c r="E81" s="10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.016</v>
       </c>
       <c r="F81" s="10" t="inlineStr"/>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -6637,12 +6626,12 @@
         </is>
       </c>
       <c r="E82" s="10" t="n">
-        <v>0.02</v>
+        <v>0.027</v>
       </c>
       <c r="F82" s="10" t="inlineStr"/>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6653,12 @@
         </is>
       </c>
       <c r="E83" s="10" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="F83" s="10" t="inlineStr"/>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6680,12 @@
         </is>
       </c>
       <c r="E84" s="10" t="n">
-        <v>0.022</v>
+        <v>0.033</v>
       </c>
       <c r="F84" s="10" t="inlineStr"/>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -6718,12 +6707,12 @@
         </is>
       </c>
       <c r="E85" s="10" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="F85" s="10" t="inlineStr"/>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -6745,12 +6734,12 @@
         </is>
       </c>
       <c r="E86" s="10" t="n">
-        <v>0.028</v>
+        <v>0.082</v>
       </c>
       <c r="F86" s="10" t="inlineStr"/>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -6772,12 +6761,12 @@
         </is>
       </c>
       <c r="E87" s="10" t="n">
-        <v>0.042</v>
+        <v>0.056</v>
       </c>
       <c r="F87" s="10" t="inlineStr"/>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6788,12 @@
         </is>
       </c>
       <c r="E88" s="10" t="n">
-        <v>0.024</v>
+        <v>0.032</v>
       </c>
       <c r="F88" s="10" t="inlineStr"/>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -6826,12 +6815,12 @@
         </is>
       </c>
       <c r="E89" s="10" t="n">
-        <v>0.037</v>
+        <v>0.043</v>
       </c>
       <c r="F89" s="10" t="inlineStr"/>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -6853,12 +6842,12 @@
         </is>
       </c>
       <c r="E90" s="10" t="n">
-        <v>0.027</v>
+        <v>0.037</v>
       </c>
       <c r="F90" s="10" t="inlineStr"/>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -6880,12 +6869,12 @@
         </is>
       </c>
       <c r="E91" s="10" t="n">
-        <v>0.036</v>
+        <v>0.055</v>
       </c>
       <c r="F91" s="10" t="inlineStr"/>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -6907,12 +6896,12 @@
         </is>
       </c>
       <c r="E92" s="10" t="n">
-        <v>0.014</v>
+        <v>0.029</v>
       </c>
       <c r="F92" s="10" t="inlineStr"/>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -6934,12 +6923,12 @@
         </is>
       </c>
       <c r="E93" s="10" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="F93" s="10" t="inlineStr"/>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -6961,12 +6950,12 @@
         </is>
       </c>
       <c r="E94" s="10" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="F94" s="10" t="inlineStr"/>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6977,12 @@
         </is>
       </c>
       <c r="E95" s="10" t="n">
-        <v>0.027</v>
+        <v>0.018</v>
       </c>
       <c r="F95" s="10" t="inlineStr"/>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -7015,12 +7004,12 @@
         </is>
       </c>
       <c r="E96" s="10" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="F96" s="10" t="inlineStr"/>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -7042,12 +7031,12 @@
         </is>
       </c>
       <c r="E97" s="10" t="n">
-        <v>0.62</v>
+        <v>1.353</v>
       </c>
       <c r="F97" s="10" t="inlineStr"/>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:26</t>
+          <t>2026-04-09T06:42:26</t>
         </is>
       </c>
     </row>
@@ -7069,12 +7058,12 @@
         </is>
       </c>
       <c r="E98" s="10" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F98" s="10" t="inlineStr"/>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -7096,12 +7085,12 @@
         </is>
       </c>
       <c r="E99" s="10" t="n">
-        <v>0.015</v>
+        <v>0.021</v>
       </c>
       <c r="F99" s="10" t="inlineStr"/>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7112,12 @@
         </is>
       </c>
       <c r="E100" s="10" t="n">
-        <v>0.019</v>
+        <v>0.04</v>
       </c>
       <c r="F100" s="10" t="inlineStr"/>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -7150,12 +7139,12 @@
         </is>
       </c>
       <c r="E101" s="10" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="F101" s="10" t="inlineStr"/>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -7177,12 +7166,12 @@
         </is>
       </c>
       <c r="E102" s="10" t="n">
-        <v>0.036</v>
+        <v>0.135</v>
       </c>
       <c r="F102" s="10" t="inlineStr"/>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -7204,12 +7193,12 @@
         </is>
       </c>
       <c r="E103" s="10" t="n">
-        <v>0.029</v>
+        <v>0.063</v>
       </c>
       <c r="F103" s="10" t="inlineStr"/>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -7231,12 +7220,12 @@
         </is>
       </c>
       <c r="E104" s="10" t="n">
-        <v>0.033</v>
+        <v>0.057</v>
       </c>
       <c r="F104" s="10" t="inlineStr"/>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -7258,12 +7247,12 @@
         </is>
       </c>
       <c r="E105" s="10" t="n">
-        <v>0.042</v>
+        <v>0.037</v>
       </c>
       <c r="F105" s="10" t="inlineStr"/>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -7285,12 +7274,12 @@
         </is>
       </c>
       <c r="E106" s="10" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
       <c r="F106" s="10" t="inlineStr"/>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -7312,12 +7301,12 @@
         </is>
       </c>
       <c r="E107" s="10" t="n">
-        <v>0.029</v>
+        <v>0.02</v>
       </c>
       <c r="F107" s="10" t="inlineStr"/>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:33</t>
+          <t>2026-04-09T06:42:40</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7328,12 @@
         </is>
       </c>
       <c r="E108" s="10" t="n">
-        <v>0.012</v>
+        <v>0.021</v>
       </c>
       <c r="F108" s="10" t="inlineStr"/>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -7366,12 +7355,12 @@
         </is>
       </c>
       <c r="E109" s="10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.038</v>
       </c>
       <c r="F109" s="10" t="inlineStr"/>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7382,12 @@
         </is>
       </c>
       <c r="E110" s="10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="F110" s="10" t="inlineStr"/>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -7420,12 +7409,12 @@
         </is>
       </c>
       <c r="E111" s="10" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="F111" s="10" t="inlineStr"/>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:34</t>
+          <t>2026-04-09T06:42:41</t>
         </is>
       </c>
     </row>
@@ -7447,12 +7436,12 @@
         </is>
       </c>
       <c r="E112" s="10" t="n">
-        <v>0.018</v>
+        <v>0.138</v>
       </c>
       <c r="F112" s="10" t="inlineStr"/>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:34</t>
+          <t>2026-04-09T06:42:41</t>
         </is>
       </c>
     </row>
@@ -7474,12 +7463,12 @@
         </is>
       </c>
       <c r="E113" s="10" t="n">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="F113" s="10" t="inlineStr"/>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:34</t>
+          <t>2026-04-09T06:42:41</t>
         </is>
       </c>
     </row>
@@ -7501,12 +7490,12 @@
         </is>
       </c>
       <c r="E114" s="10" t="n">
-        <v>0.017</v>
+        <v>0.038</v>
       </c>
       <c r="F114" s="10" t="inlineStr"/>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:34</t>
+          <t>2026-04-09T06:42:41</t>
         </is>
       </c>
     </row>
@@ -7528,12 +7517,12 @@
         </is>
       </c>
       <c r="E115" s="10" t="n">
-        <v>0.039</v>
+        <v>0.031</v>
       </c>
       <c r="F115" s="10" t="inlineStr"/>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:34</t>
+          <t>2026-04-09T06:42:41</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7544,12 @@
         </is>
       </c>
       <c r="E116" s="10" t="n">
-        <v>0.03</v>
+        <v>0.068</v>
       </c>
       <c r="F116" s="10" t="inlineStr"/>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:34</t>
+          <t>2026-04-09T06:42:41</t>
         </is>
       </c>
     </row>
@@ -7582,12 +7571,12 @@
         </is>
       </c>
       <c r="E117" s="10" t="n">
-        <v>0.028</v>
+        <v>0.041</v>
       </c>
       <c r="F117" s="10" t="inlineStr"/>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:34</t>
+          <t>2026-04-09T06:42:41</t>
         </is>
       </c>
     </row>
@@ -7609,12 +7598,12 @@
         </is>
       </c>
       <c r="E118" s="10" t="n">
-        <v>0.026</v>
+        <v>0.036</v>
       </c>
       <c r="F118" s="10" t="inlineStr"/>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:34</t>
+          <t>2026-04-09T06:42:41</t>
         </is>
       </c>
     </row>
@@ -7636,12 +7625,12 @@
         </is>
       </c>
       <c r="E119" s="10" t="n">
-        <v>0.025</v>
+        <v>0.043</v>
       </c>
       <c r="F119" s="10" t="inlineStr"/>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:34</t>
+          <t>2026-04-09T06:42:41</t>
         </is>
       </c>
     </row>
@@ -7663,12 +7652,12 @@
         </is>
       </c>
       <c r="E120" s="10" t="n">
-        <v>0.045</v>
+        <v>0.032</v>
       </c>
       <c r="F120" s="10" t="inlineStr"/>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:34</t>
+          <t>2026-04-09T06:42:41</t>
         </is>
       </c>
     </row>
@@ -7690,12 +7679,12 @@
         </is>
       </c>
       <c r="E121" s="10" t="n">
-        <v>0.044</v>
+        <v>0.158</v>
       </c>
       <c r="F121" s="10" t="inlineStr"/>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:34</t>
+          <t>2026-04-09T06:42:41</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7706,12 @@
         </is>
       </c>
       <c r="E122" s="10" t="n">
-        <v>0.018</v>
+        <v>0.028</v>
       </c>
       <c r="F122" s="10" t="inlineStr"/>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:34</t>
+          <t>2026-04-09T06:42:41</t>
         </is>
       </c>
     </row>
@@ -7744,12 +7733,12 @@
         </is>
       </c>
       <c r="E123" s="10" t="n">
-        <v>0.026</v>
+        <v>0.042</v>
       </c>
       <c r="F123" s="10" t="inlineStr"/>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -7771,12 +7760,12 @@
         </is>
       </c>
       <c r="E124" s="10" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="F124" s="10" t="inlineStr"/>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -7798,12 +7787,12 @@
         </is>
       </c>
       <c r="E125" s="10" t="n">
-        <v>0.016</v>
+        <v>0.026</v>
       </c>
       <c r="F125" s="10" t="inlineStr"/>
       <c r="G125" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
@@ -7825,18 +7814,21 @@
         </is>
       </c>
       <c r="E126" s="10" t="n">
-        <v>0.013</v>
+        <v>0.019</v>
       </c>
       <c r="F126" s="10" t="inlineStr"/>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09T05:27:35</t>
+          <t>2026-04-09T06:42:43</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="잘못된 값" error="PASS, FAIL, ERROR, SKIP 중 하나여야 합니다." promptTitle="결과" prompt="테스트 결과를 선택하세요." type="list">
+      <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"PASS,FAIL,ERROR,SKIP"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
